--- a/exports/tours_Friday,_May_29.xlsx
+++ b/exports/tours_Friday,_May_29.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>3:00 AM</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
